--- a/data/RPL 6 Predictor Answer Master.xlsx
+++ b/data/RPL 6 Predictor Answer Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckinsey-my.sharepoint.com/personal/vinod_krishnan_external_mckinsey_com/Documents/Desktop/rpl6-predictor-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E164543-B273-4FA0-938B-F09326E1AB62}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973018EF-FF06-42E8-B745-77D9E910A011}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CEABAB56-9726-4D02-8BFD-74E940918907}"/>
   </bookViews>
@@ -928,6 +928,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -945,9 +948,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1376,158 +1376,158 @@
   <sheetData>
     <row r="1" spans="1:84" x14ac:dyDescent="0.3">
       <c r="F1" s="8"/>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="24" t="s">
+      <c r="J1" s="26"/>
+      <c r="K1" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="24" t="s">
+      <c r="L1" s="26"/>
+      <c r="M1" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="N1" s="25"/>
-      <c r="O1" s="28" t="s">
+      <c r="N1" s="26"/>
+      <c r="O1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="28" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="29"/>
-      <c r="S1" s="24" t="s">
+      <c r="R1" s="30"/>
+      <c r="S1" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="T1" s="25"/>
-      <c r="U1" s="24" t="s">
+      <c r="T1" s="26"/>
+      <c r="U1" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="V1" s="25"/>
-      <c r="W1" s="24" t="s">
+      <c r="V1" s="26"/>
+      <c r="W1" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="24" t="s">
+      <c r="X1" s="26"/>
+      <c r="Y1" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="24" t="s">
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="24" t="s">
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="26" t="s">
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="24" t="s">
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="24" t="s">
+      <c r="AH1" s="26"/>
+      <c r="AI1" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="24" t="s">
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="AL1" s="25"/>
-      <c r="AM1" s="24" t="s">
+      <c r="AL1" s="26"/>
+      <c r="AM1" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="AN1" s="25"/>
-      <c r="AO1" s="24" t="s">
+      <c r="AN1" s="26"/>
+      <c r="AO1" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="24" t="s">
+      <c r="AP1" s="26"/>
+      <c r="AQ1" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="AR1" s="25"/>
-      <c r="AS1" s="24" t="s">
+      <c r="AR1" s="26"/>
+      <c r="AS1" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="AT1" s="25"/>
-      <c r="AU1" s="24" t="s">
+      <c r="AT1" s="26"/>
+      <c r="AU1" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="24" t="s">
+      <c r="AV1" s="26"/>
+      <c r="AW1" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="AX1" s="25"/>
-      <c r="AY1" s="24" t="s">
+      <c r="AX1" s="26"/>
+      <c r="AY1" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="AZ1" s="25"/>
-      <c r="BA1" s="24" t="s">
+      <c r="AZ1" s="26"/>
+      <c r="BA1" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="BB1" s="25"/>
-      <c r="BC1" s="24" t="s">
+      <c r="BB1" s="26"/>
+      <c r="BC1" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="BD1" s="25"/>
-      <c r="BE1" s="24" t="s">
+      <c r="BD1" s="26"/>
+      <c r="BE1" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="BF1" s="25"/>
-      <c r="BG1" s="24" t="s">
+      <c r="BF1" s="26"/>
+      <c r="BG1" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="BH1" s="25"/>
-      <c r="BI1" s="24" t="s">
+      <c r="BH1" s="26"/>
+      <c r="BI1" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="BJ1" s="25"/>
-      <c r="BK1" s="24" t="s">
+      <c r="BJ1" s="26"/>
+      <c r="BK1" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="BL1" s="25"/>
-      <c r="BM1" s="24" t="s">
+      <c r="BL1" s="26"/>
+      <c r="BM1" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="BN1" s="25"/>
-      <c r="BO1" s="24" t="s">
+      <c r="BN1" s="26"/>
+      <c r="BO1" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="BP1" s="25"/>
-      <c r="BQ1" s="24" t="s">
+      <c r="BP1" s="26"/>
+      <c r="BQ1" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="BR1" s="25"/>
-      <c r="BS1" s="24" t="s">
+      <c r="BR1" s="26"/>
+      <c r="BS1" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="BT1" s="25"/>
-      <c r="BU1" s="24" t="s">
+      <c r="BT1" s="26"/>
+      <c r="BU1" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="BV1" s="25"/>
-      <c r="BW1" s="24" t="s">
+      <c r="BV1" s="26"/>
+      <c r="BW1" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="BX1" s="25"/>
-      <c r="BY1" s="24" t="s">
+      <c r="BX1" s="26"/>
+      <c r="BY1" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="BZ1" s="25"/>
-      <c r="CA1" s="24" t="s">
+      <c r="BZ1" s="26"/>
+      <c r="CA1" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="CB1" s="25"/>
-      <c r="CC1" s="24" t="s">
+      <c r="CB1" s="26"/>
+      <c r="CC1" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="CD1" s="25"/>
-      <c r="CE1" s="24" t="s">
+      <c r="CD1" s="26"/>
+      <c r="CE1" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="CF1" s="25"/>
+      <c r="CF1" s="26"/>
     </row>
     <row r="2" spans="1:84" s="23" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
@@ -1557,7 +1557,7 @@
       <c r="I2" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="24" t="s">
         <v>146</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -1806,8 +1806,8 @@
         <v>0.63157894736842102</v>
       </c>
       <c r="H3" s="11">
-        <f>SUM(J3,L3,N3,P3,R3,T3,V3,X3,Z3,AB3,AD3,AF3,AH3,AJ3,AL3,AN3,AP3,AR3,AT3,AV3,AX3,AZ3,BB3,BD3,BF3,BH3,BJ3,BL3,BN3,BP3,BR3,BT3,BV3,BX3,BZ3,CB3,CD3,CF3)</f>
-        <v>10</v>
+        <f t="shared" ref="H3:H34" si="0">SUM(J3,L3,N3,P3,R3,T3,V3,X3,Z3,AB3,AD3,AF3,AH3,AJ3,AL3,AN3,AP3,AR3,AT3,AV3,AX3,AZ3,BB3,BD3,BF3,BH3,BJ3,BL3,BN3,BP3,BR3,BT3,BV3,BX3,BZ3,CB3,CD3,CF3)</f>
+        <v>11</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>14</v>
@@ -1839,7 +1839,7 @@
         <v>7</v>
       </c>
       <c r="V3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="13" t="s">
         <v>6</v>
@@ -2051,8 +2051,8 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H4" s="11">
-        <f>SUM(J4,L4,N4,P4,R4,T4,V4,X4,Z4,AB4,AD4,AF4,AH4,AJ4,AL4,AN4,AP4,AR4,AT4,AV4,AX4,AZ4,BB4,BD4,BF4,BH4,BJ4,BL4,BN4,BP4,BR4,BT4,BV4,BX4,BZ4,CB4,CD4,CF4)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>14</v>
@@ -2094,7 +2094,7 @@
         <v>7</v>
       </c>
       <c r="V4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="13" t="s">
         <v>6</v>
@@ -2306,8 +2306,8 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H5" s="11">
-        <f>SUM(J5,L5,N5,P5,R5,T5,V5,X5,Z5,AB5,AD5,AF5,AH5,AJ5,AL5,AN5,AP5,AR5,AT5,AV5,AX5,AZ5,BB5,BD5,BF5,BH5,BJ5,BL5,BN5,BP5,BR5,BT5,BV5,BX5,BZ5,CB5,CD5,CF5)</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>14</v>
@@ -2349,7 +2349,7 @@
         <v>5</v>
       </c>
       <c r="V5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" s="13" t="s">
         <v>6</v>
@@ -2547,9 +2547,7 @@
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
-      <c r="E6" s="9">
-        <v>1</v>
-      </c>
+      <c r="E6" s="9"/>
       <c r="F6" s="6">
         <v>0</v>
       </c>
@@ -2557,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="11">
-        <f>SUM(J6,L6,N6,P6,R6,T6,V6,X6,Z6,AB6,AD6,AF6,AH6,AJ6,AL6,AN6,AP6,AR6,AT6,AV6,AX6,AZ6,BB6,BD6,BF6,BH6,BJ6,BL6,BN6,BP6,BR6,BT6,BV6,BX6,BZ6,CB6,CD6,CF6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I6" s="9"/>
@@ -2796,8 +2794,8 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H7" s="11">
-        <f>SUM(J7,L7,N7,P7,R7,T7,V7,X7,Z7,AB7,AD7,AF7,AH7,AJ7,AL7,AN7,AP7,AR7,AT7,AV7,AX7,AZ7,BB7,BD7,BF7,BH7,BJ7,BL7,BN7,BP7,BR7,BT7,BV7,BX7,BZ7,CB7,CD7,CF7)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>14</v>
@@ -2839,7 +2837,7 @@
         <v>7</v>
       </c>
       <c r="V7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="13" t="s">
         <v>6</v>
@@ -3051,8 +3049,8 @@
         <v>0.89473684210526316</v>
       </c>
       <c r="H8" s="11">
-        <f>SUM(J8,L8,N8,P8,R8,T8,V8,X8,Z8,AB8,AD8,AF8,AH8,AJ8,AL8,AN8,AP8,AR8,AT8,AV8,AX8,AZ8,BB8,BD8,BF8,BH8,BJ8,BL8,BN8,BP8,BR8,BT8,BV8,BX8,BZ8,CB8,CD8,CF8)</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>14</v>
@@ -3092,7 +3090,7 @@
         <v>5</v>
       </c>
       <c r="V8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="13" t="s">
         <v>6</v>
@@ -3304,8 +3302,8 @@
         <v>0.68421052631578949</v>
       </c>
       <c r="H9" s="11">
-        <f>SUM(J9,L9,N9,P9,R9,T9,V9,X9,Z9,AB9,AD9,AF9,AH9,AJ9,AL9,AN9,AP9,AR9,AT9,AV9,AX9,AZ9,BB9,BD9,BF9,BH9,BJ9,BL9,BN9,BP9,BR9,BT9,BV9,BX9,BZ9,CB9,CD9,CF9)</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>14</v>
@@ -3345,7 +3343,7 @@
         <v>7</v>
       </c>
       <c r="V9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="13" t="s">
         <v>6</v>
@@ -3557,8 +3555,8 @@
         <v>1</v>
       </c>
       <c r="H10" s="11">
-        <f>SUM(J10,L10,N10,P10,R10,T10,V10,X10,Z10,AB10,AD10,AF10,AH10,AJ10,AL10,AN10,AP10,AR10,AT10,AV10,AX10,AZ10,BB10,BD10,BF10,BH10,BJ10,BL10,BN10,BP10,BR10,BT10,BV10,BX10,BZ10,CB10,CD10,CF10)</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>14</v>
@@ -3600,7 +3598,7 @@
         <v>5</v>
       </c>
       <c r="V10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" s="13">
         <v>3</v>
@@ -3812,7 +3810,7 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H11" s="11">
-        <f>SUM(J11,L11,N11,P11,R11,T11,V11,X11,Z11,AB11,AD11,AF11,AH11,AJ11,AL11,AN11,AP11,AR11,AT11,AV11,AX11,AZ11,BB11,BD11,BF11,BH11,BJ11,BL11,BN11,BP11,BR11,BT11,BV11,BX11,BZ11,CB11,CD11,CF11)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="I11" s="9" t="s">
@@ -4067,8 +4065,8 @@
         <v>0.52631578947368418</v>
       </c>
       <c r="H12" s="11">
-        <f>SUM(J12,L12,N12,P12,R12,T12,V12,X12,Z12,AB12,AD12,AF12,AH12,AJ12,AL12,AN12,AP12,AR12,AT12,AV12,AX12,AZ12,BB12,BD12,BF12,BH12,BJ12,BL12,BN12,BP12,BR12,BT12,BV12,BX12,BZ12,CB12,CD12,CF12)</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="5">
@@ -4102,7 +4100,7 @@
         <v>5</v>
       </c>
       <c r="V12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="13">
         <v>2</v>
@@ -4314,8 +4312,8 @@
         <v>0.92105263157894735</v>
       </c>
       <c r="H13" s="11">
-        <f>SUM(J13,L13,N13,P13,R13,T13,V13,X13,Z13,AB13,AD13,AF13,AH13,AJ13,AL13,AN13,AP13,AR13,AT13,AV13,AX13,AZ13,BB13,BD13,BF13,BH13,BJ13,BL13,BN13,BP13,BR13,BT13,BV13,BX13,BZ13,CB13,CD13,CF13)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>14</v>
@@ -4357,7 +4355,7 @@
         <v>5</v>
       </c>
       <c r="V13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="13" t="s">
         <v>6</v>
@@ -4569,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="11">
-        <f>SUM(J14,L14,N14,P14,R14,T14,V14,X14,Z14,AB14,AD14,AF14,AH14,AJ14,AL14,AN14,AP14,AR14,AT14,AV14,AX14,AZ14,BB14,BD14,BF14,BH14,BJ14,BL14,BN14,BP14,BR14,BT14,BV14,BX14,BZ14,CB14,CD14,CF14)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I14" s="9" t="s">
@@ -4824,8 +4822,8 @@
         <v>0.89473684210526316</v>
       </c>
       <c r="H15" s="11">
-        <f>SUM(J15,L15,N15,P15,R15,T15,V15,X15,Z15,AB15,AD15,AF15,AH15,AJ15,AL15,AN15,AP15,AR15,AT15,AV15,AX15,AZ15,BB15,BD15,BF15,BH15,BJ15,BL15,BN15,BP15,BR15,BT15,BV15,BX15,BZ15,CB15,CD15,CF15)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>14</v>
@@ -4865,7 +4863,7 @@
         <v>7</v>
       </c>
       <c r="V15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="13" t="s">
         <v>6</v>
@@ -5077,8 +5075,8 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="H16" s="11">
-        <f>SUM(J16,L16,N16,P16,R16,T16,V16,X16,Z16,AB16,AD16,AF16,AH16,AJ16,AL16,AN16,AP16,AR16,AT16,AV16,AX16,AZ16,BB16,BD16,BF16,BH16,BJ16,BL16,BN16,BP16,BR16,BT16,BV16,BX16,BZ16,CB16,CD16,CF16)</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5">
@@ -5108,7 +5106,7 @@
         <v>7</v>
       </c>
       <c r="V16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="13" t="s">
         <v>4</v>
@@ -5320,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="11">
-        <f>SUM(J17,L17,N17,P17,R17,T17,V17,X17,Z17,AB17,AD17,AF17,AH17,AJ17,AL17,AN17,AP17,AR17,AT17,AV17,AX17,AZ17,BB17,BD17,BF17,BH17,BJ17,BL17,BN17,BP17,BR17,BT17,BV17,BX17,BZ17,CB17,CD17,CF17)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="I17" s="9" t="s">
@@ -5575,8 +5573,8 @@
         <v>0.86842105263157898</v>
       </c>
       <c r="H18" s="11">
-        <f>SUM(J18,L18,N18,P18,R18,T18,V18,X18,Z18,AB18,AD18,AF18,AH18,AJ18,AL18,AN18,AP18,AR18,AT18,AV18,AX18,AZ18,BB18,BD18,BF18,BH18,BJ18,BL18,BN18,BP18,BR18,BT18,BV18,BX18,BZ18,CB18,CD18,CF18)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>14</v>
@@ -5612,7 +5610,7 @@
         <v>7</v>
       </c>
       <c r="V18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="13">
         <v>2</v>
@@ -5824,8 +5822,8 @@
         <v>0.92105263157894735</v>
       </c>
       <c r="H19" s="11">
-        <f>SUM(J19,L19,N19,P19,R19,T19,V19,X19,Z19,AB19,AD19,AF19,AH19,AJ19,AL19,AN19,AP19,AR19,AT19,AV19,AX19,AZ19,BB19,BD19,BF19,BH19,BJ19,BL19,BN19,BP19,BR19,BT19,BV19,BX19,BZ19,CB19,CD19,CF19)</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>13</v>
@@ -5867,7 +5865,7 @@
         <v>5</v>
       </c>
       <c r="V19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="13" t="s">
         <v>6</v>
@@ -6079,7 +6077,7 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H20" s="11">
-        <f>SUM(J20,L20,N20,P20,R20,T20,V20,X20,Z20,AB20,AD20,AF20,AH20,AJ20,AL20,AN20,AP20,AR20,AT20,AV20,AX20,AZ20,BB20,BD20,BF20,BH20,BJ20,BL20,BN20,BP20,BR20,BT20,BV20,BX20,BZ20,CB20,CD20,CF20)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="I20" s="9" t="s">
@@ -6334,8 +6332,8 @@
         <v>0.57894736842105265</v>
       </c>
       <c r="H21" s="11">
-        <f>SUM(J21,L21,N21,P21,R21,T21,V21,X21,Z21,AB21,AD21,AF21,AH21,AJ21,AL21,AN21,AP21,AR21,AT21,AV21,AX21,AZ21,BB21,BD21,BF21,BH21,BJ21,BL21,BN21,BP21,BR21,BT21,BV21,BX21,BZ21,CB21,CD21,CF21)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>13</v>
@@ -6377,7 +6375,7 @@
         <v>5</v>
       </c>
       <c r="V21" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="13">
         <v>2</v>
@@ -6589,8 +6587,8 @@
         <v>0.86842105263157898</v>
       </c>
       <c r="H22" s="11">
-        <f>SUM(J22,L22,N22,P22,R22,T22,V22,X22,Z22,AB22,AD22,AF22,AH22,AJ22,AL22,AN22,AP22,AR22,AT22,AV22,AX22,AZ22,BB22,BD22,BF22,BH22,BJ22,BL22,BN22,BP22,BR22,BT22,BV22,BX22,BZ22,CB22,CD22,CF22)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>13</v>
@@ -6624,7 +6622,7 @@
         <v>5</v>
       </c>
       <c r="V22" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>6</v>
@@ -6836,8 +6834,8 @@
         <v>1</v>
       </c>
       <c r="H23" s="11">
-        <f>SUM(J23,L23,N23,P23,R23,T23,V23,X23,Z23,AB23,AD23,AF23,AH23,AJ23,AL23,AN23,AP23,AR23,AT23,AV23,AX23,AZ23,BB23,BD23,BF23,BH23,BJ23,BL23,BN23,BP23,BR23,BT23,BV23,BX23,BZ23,CB23,CD23,CF23)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>14</v>
@@ -6879,7 +6877,7 @@
         <v>7</v>
       </c>
       <c r="V23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="13" t="s">
         <v>6</v>
@@ -7091,8 +7089,8 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H24" s="11">
-        <f>SUM(J24,L24,N24,P24,R24,T24,V24,X24,Z24,AB24,AD24,AF24,AH24,AJ24,AL24,AN24,AP24,AR24,AT24,AV24,AX24,AZ24,BB24,BD24,BF24,BH24,BJ24,BL24,BN24,BP24,BR24,BT24,BV24,BX24,BZ24,CB24,CD24,CF24)</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>13</v>
@@ -7134,7 +7132,7 @@
         <v>7</v>
       </c>
       <c r="V24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="13">
         <v>3</v>
@@ -7346,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="11">
-        <f>SUM(J25,L25,N25,P25,R25,T25,V25,X25,Z25,AB25,AD25,AF25,AH25,AJ25,AL25,AN25,AP25,AR25,AT25,AV25,AX25,AZ25,BB25,BD25,BF25,BH25,BJ25,BL25,BN25,BP25,BR25,BT25,BV25,BX25,BZ25,CB25,CD25,CF25)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="I25" s="9" t="s">
@@ -7601,8 +7599,8 @@
         <v>0.92105263157894735</v>
       </c>
       <c r="H26" s="11">
-        <f>SUM(J26,L26,N26,P26,R26,T26,V26,X26,Z26,AB26,AD26,AF26,AH26,AJ26,AL26,AN26,AP26,AR26,AT26,AV26,AX26,AZ26,BB26,BD26,BF26,BH26,BJ26,BL26,BN26,BP26,BR26,BT26,BV26,BX26,BZ26,CB26,CD26,CF26)</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="5">
@@ -7642,7 +7640,7 @@
         <v>5</v>
       </c>
       <c r="V26" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="13" t="s">
         <v>6</v>
@@ -7850,8 +7848,8 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H27" s="11">
-        <f>SUM(J27,L27,N27,P27,R27,T27,V27,X27,Z27,AB27,AD27,AF27,AH27,AJ27,AL27,AN27,AP27,AR27,AT27,AV27,AX27,AZ27,BB27,BD27,BF27,BH27,BJ27,BL27,BN27,BP27,BR27,BT27,BV27,BX27,BZ27,CB27,CD27,CF27)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>14</v>
@@ -7893,7 +7891,7 @@
         <v>5</v>
       </c>
       <c r="V27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" s="13">
         <v>3</v>
@@ -8105,8 +8103,8 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H28" s="11">
-        <f>SUM(J28,L28,N28,P28,R28,T28,V28,X28,Z28,AB28,AD28,AF28,AH28,AJ28,AL28,AN28,AP28,AR28,AT28,AV28,AX28,AZ28,BB28,BD28,BF28,BH28,BJ28,BL28,BN28,BP28,BR28,BT28,BV28,BX28,BZ28,CB28,CD28,CF28)</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>14</v>
@@ -8148,7 +8146,7 @@
         <v>5</v>
       </c>
       <c r="V28" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="13" t="s">
         <v>1</v>
@@ -8354,7 +8352,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="11">
-        <f>SUM(J29,L29,N29,P29,R29,T29,V29,X29,Z29,AB29,AD29,AF29,AH29,AJ29,AL29,AN29,AP29,AR29,AT29,AV29,AX29,AZ29,BB29,BD29,BF29,BH29,BJ29,BL29,BN29,BP29,BR29,BT29,BV29,BX29,BZ29,CB29,CD29,CF29)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I29" s="9"/>
@@ -8595,7 +8593,7 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H30" s="11">
-        <f>SUM(J30,L30,N30,P30,R30,T30,V30,X30,Z30,AB30,AD30,AF30,AH30,AJ30,AL30,AN30,AP30,AR30,AT30,AV30,AX30,AZ30,BB30,BD30,BF30,BH30,BJ30,BL30,BN30,BP30,BR30,BT30,BV30,BX30,BZ30,CB30,CD30,CF30)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="I30" s="9" t="s">
@@ -8850,7 +8848,7 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H31" s="11">
-        <f>SUM(J31,L31,N31,P31,R31,T31,V31,X31,Z31,AB31,AD31,AF31,AH31,AJ31,AL31,AN31,AP31,AR31,AT31,AV31,AX31,AZ31,BB31,BD31,BF31,BH31,BJ31,BL31,BN31,BP31,BR31,BT31,BV31,BX31,BZ31,CB31,CD31,CF31)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="I31" s="9" t="s">
@@ -9103,8 +9101,8 @@
         <v>0.86842105263157898</v>
       </c>
       <c r="H32" s="11">
-        <f>SUM(J32,L32,N32,P32,R32,T32,V32,X32,Z32,AB32,AD32,AF32,AH32,AJ32,AL32,AN32,AP32,AR32,AT32,AV32,AX32,AZ32,BB32,BD32,BF32,BH32,BJ32,BL32,BN32,BP32,BR32,BT32,BV32,BX32,BZ32,CB32,CD32,CF32)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>14</v>
@@ -9146,7 +9144,7 @@
         <v>5</v>
       </c>
       <c r="V32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" s="13" t="s">
         <v>6</v>
@@ -9358,8 +9356,8 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H33" s="11">
-        <f>SUM(J33,L33,N33,P33,R33,T33,V33,X33,Z33,AB33,AD33,AF33,AH33,AJ33,AL33,AN33,AP33,AR33,AT33,AV33,AX33,AZ33,BB33,BD33,BF33,BH33,BJ33,BL33,BN33,BP33,BR33,BT33,BV33,BX33,BZ33,CB33,CD33,CF33)</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>14</v>
@@ -9401,7 +9399,7 @@
         <v>7</v>
       </c>
       <c r="V33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="13">
         <v>2</v>
@@ -9613,8 +9611,8 @@
         <v>0.86842105263157898</v>
       </c>
       <c r="H34" s="11">
-        <f>SUM(J34,L34,N34,P34,R34,T34,V34,X34,Z34,AB34,AD34,AF34,AH34,AJ34,AL34,AN34,AP34,AR34,AT34,AV34,AX34,AZ34,BB34,BD34,BF34,BH34,BJ34,BL34,BN34,BP34,BR34,BT34,BV34,BX34,BZ34,CB34,CD34,CF34)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="5">
@@ -9650,7 +9648,7 @@
         <v>7</v>
       </c>
       <c r="V34" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="13">
         <v>3</v>
@@ -9862,8 +9860,8 @@
         <v>0.94736842105263153</v>
       </c>
       <c r="H35" s="11">
-        <f>SUM(J35,L35,N35,P35,R35,T35,V35,X35,Z35,AB35,AD35,AF35,AH35,AJ35,AL35,AN35,AP35,AR35,AT35,AV35,AX35,AZ35,BB35,BD35,BF35,BH35,BJ35,BL35,BN35,BP35,BR35,BT35,BV35,BX35,BZ35,CB35,CD35,CF35)</f>
-        <v>12</v>
+        <f t="shared" ref="H35:H52" si="1">SUM(J35,L35,N35,P35,R35,T35,V35,X35,Z35,AB35,AD35,AF35,AH35,AJ35,AL35,AN35,AP35,AR35,AT35,AV35,AX35,AZ35,BB35,BD35,BF35,BH35,BJ35,BL35,BN35,BP35,BR35,BT35,BV35,BX35,BZ35,CB35,CD35,CF35)</f>
+        <v>11</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>14</v>
@@ -9903,7 +9901,7 @@
         <v>5</v>
       </c>
       <c r="V35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" s="13" t="s">
         <v>6</v>
@@ -10115,8 +10113,8 @@
         <v>0.84210526315789469</v>
       </c>
       <c r="H36" s="11">
-        <f>SUM(J36,L36,N36,P36,R36,T36,V36,X36,Z36,AB36,AD36,AF36,AH36,AJ36,AL36,AN36,AP36,AR36,AT36,AV36,AX36,AZ36,BB36,BD36,BF36,BH36,BJ36,BL36,BN36,BP36,BR36,BT36,BV36,BX36,BZ36,CB36,CD36,CF36)</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>14</v>
@@ -10152,7 +10150,7 @@
         <v>5</v>
       </c>
       <c r="V36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" s="13">
         <v>3</v>
@@ -10364,7 +10362,7 @@
         <v>0.39473684210526316</v>
       </c>
       <c r="H37" s="11">
-        <f>SUM(J37,L37,N37,P37,R37,T37,V37,X37,Z37,AB37,AD37,AF37,AH37,AJ37,AL37,AN37,AP37,AR37,AT37,AV37,AX37,AZ37,BB37,BD37,BF37,BH37,BJ37,BL37,BN37,BP37,BR37,BT37,BV37,BX37,BZ37,CB37,CD37,CF37)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="I37" s="9"/>
@@ -10607,7 +10605,7 @@
         <v>0.81578947368421051</v>
       </c>
       <c r="H38" s="11">
-        <f>SUM(J38,L38,N38,P38,R38,T38,V38,X38,Z38,AB38,AD38,AF38,AH38,AJ38,AL38,AN38,AP38,AR38,AT38,AV38,AX38,AZ38,BB38,BD38,BF38,BH38,BJ38,BL38,BN38,BP38,BR38,BT38,BV38,BX38,BZ38,CB38,CD38,CF38)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="I38" s="9" t="s">
@@ -10862,8 +10860,8 @@
         <v>0.78947368421052633</v>
       </c>
       <c r="H39" s="11">
-        <f>SUM(J39,L39,N39,P39,R39,T39,V39,X39,Z39,AB39,AD39,AF39,AH39,AJ39,AL39,AN39,AP39,AR39,AT39,AV39,AX39,AZ39,BB39,BD39,BF39,BH39,BJ39,BL39,BN39,BP39,BR39,BT39,BV39,BX39,BZ39,CB39,CD39,CF39)</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>14</v>
@@ -10905,7 +10903,7 @@
         <v>5</v>
       </c>
       <c r="V39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" s="13" t="s">
         <v>6</v>
@@ -11117,8 +11115,8 @@
         <v>0.57894736842105265</v>
       </c>
       <c r="H40" s="11">
-        <f>SUM(J40,L40,N40,P40,R40,T40,V40,X40,Z40,AB40,AD40,AF40,AH40,AJ40,AL40,AN40,AP40,AR40,AT40,AV40,AX40,AZ40,BB40,BD40,BF40,BH40,BJ40,BL40,BN40,BP40,BR40,BT40,BV40,BX40,BZ40,CB40,CD40,CF40)</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>14</v>
@@ -11152,7 +11150,7 @@
         <v>7</v>
       </c>
       <c r="V40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="13">
         <v>2</v>
@@ -11364,8 +11362,8 @@
         <v>1</v>
       </c>
       <c r="H41" s="11">
-        <f>SUM(J41,L41,N41,P41,R41,T41,V41,X41,Z41,AB41,AD41,AF41,AH41,AJ41,AL41,AN41,AP41,AR41,AT41,AV41,AX41,AZ41,BB41,BD41,BF41,BH41,BJ41,BL41,BN41,BP41,BR41,BT41,BV41,BX41,BZ41,CB41,CD41,CF41)</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>14</v>
@@ -11407,7 +11405,7 @@
         <v>7</v>
       </c>
       <c r="V41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="13" t="s">
         <v>6</v>
@@ -11619,8 +11617,8 @@
         <v>0.84210526315789469</v>
       </c>
       <c r="H42" s="11">
-        <f>SUM(J42,L42,N42,P42,R42,T42,V42,X42,Z42,AB42,AD42,AF42,AH42,AJ42,AL42,AN42,AP42,AR42,AT42,AV42,AX42,AZ42,BB42,BD42,BF42,BH42,BJ42,BL42,BN42,BP42,BR42,BT42,BV42,BX42,BZ42,CB42,CD42,CF42)</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>13</v>
@@ -11658,7 +11656,7 @@
         <v>5</v>
       </c>
       <c r="V42" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" s="13" t="s">
         <v>6</v>
@@ -11866,8 +11864,8 @@
         <v>0.57894736842105265</v>
       </c>
       <c r="H43" s="11">
-        <f>SUM(J43,L43,N43,P43,R43,T43,V43,X43,Z43,AB43,AD43,AF43,AH43,AJ43,AL43,AN43,AP43,AR43,AT43,AV43,AX43,AZ43,BB43,BD43,BF43,BH43,BJ43,BL43,BN43,BP43,BR43,BT43,BV43,BX43,BZ43,CB43,CD43,CF43)</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>14</v>
@@ -11899,7 +11897,7 @@
         <v>5</v>
       </c>
       <c r="V43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" s="13" t="s">
         <v>6</v>
@@ -12111,7 +12109,7 @@
         <v>0.78947368421052633</v>
       </c>
       <c r="H44" s="11">
-        <f>SUM(J44,L44,N44,P44,R44,T44,V44,X44,Z44,AB44,AD44,AF44,AH44,AJ44,AL44,AN44,AP44,AR44,AT44,AV44,AX44,AZ44,BB44,BD44,BF44,BH44,BJ44,BL44,BN44,BP44,BR44,BT44,BV44,BX44,BZ44,CB44,CD44,CF44)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="I44" s="9" t="s">
@@ -12366,8 +12364,8 @@
         <v>0.86842105263157898</v>
       </c>
       <c r="H45" s="11">
-        <f>SUM(J45,L45,N45,P45,R45,T45,V45,X45,Z45,AB45,AD45,AF45,AH45,AJ45,AL45,AN45,AP45,AR45,AT45,AV45,AX45,AZ45,BB45,BD45,BF45,BH45,BJ45,BL45,BN45,BP45,BR45,BT45,BV45,BX45,BZ45,CB45,CD45,CF45)</f>
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>13</v>
@@ -12407,7 +12405,7 @@
         <v>7</v>
       </c>
       <c r="V45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="13">
         <v>3</v>
@@ -12619,8 +12617,8 @@
         <v>1</v>
       </c>
       <c r="H46" s="11">
-        <f>SUM(J46,L46,N46,P46,R46,T46,V46,X46,Z46,AB46,AD46,AF46,AH46,AJ46,AL46,AN46,AP46,AR46,AT46,AV46,AX46,AZ46,BB46,BD46,BF46,BH46,BJ46,BL46,BN46,BP46,BR46,BT46,BV46,BX46,BZ46,CB46,CD46,CF46)</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>14</v>
@@ -12662,7 +12660,7 @@
         <v>5</v>
       </c>
       <c r="V46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="13">
         <v>2</v>
@@ -12874,8 +12872,8 @@
         <v>1</v>
       </c>
       <c r="H47" s="11">
-        <f>SUM(J47,L47,N47,P47,R47,T47,V47,X47,Z47,AB47,AD47,AF47,AH47,AJ47,AL47,AN47,AP47,AR47,AT47,AV47,AX47,AZ47,BB47,BD47,BF47,BH47,BJ47,BL47,BN47,BP47,BR47,BT47,BV47,BX47,BZ47,CB47,CD47,CF47)</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="I47" s="9" t="s">
         <v>14</v>
@@ -12917,7 +12915,7 @@
         <v>5</v>
       </c>
       <c r="V47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" s="13">
         <v>3</v>
@@ -13129,8 +13127,8 @@
         <v>0.97368421052631582</v>
       </c>
       <c r="H48" s="11">
-        <f>SUM(J48,L48,N48,P48,R48,T48,V48,X48,Z48,AB48,AD48,AF48,AH48,AJ48,AL48,AN48,AP48,AR48,AT48,AV48,AX48,AZ48,BB48,BD48,BF48,BH48,BJ48,BL48,BN48,BP48,BR48,BT48,BV48,BX48,BZ48,CB48,CD48,CF48)</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>14</v>
@@ -13172,7 +13170,7 @@
         <v>7</v>
       </c>
       <c r="V48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="13" t="s">
         <v>6</v>
@@ -13384,7 +13382,7 @@
         <v>0.18421052631578946</v>
       </c>
       <c r="H49" s="11">
-        <f>SUM(J49,L49,N49,P49,R49,T49,V49,X49,Z49,AB49,AD49,AF49,AH49,AJ49,AL49,AN49,AP49,AR49,AT49,AV49,AX49,AZ49,BB49,BD49,BF49,BH49,BJ49,BL49,BN49,BP49,BR49,BT49,BV49,BX49,BZ49,CB49,CD49,CF49)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I49" s="9"/>
@@ -13617,7 +13615,7 @@
         <v>0.65789473684210531</v>
       </c>
       <c r="H50" s="11">
-        <f>SUM(J50,L50,N50,P50,R50,T50,V50,X50,Z50,AB50,AD50,AF50,AH50,AJ50,AL50,AN50,AP50,AR50,AT50,AV50,AX50,AZ50,BB50,BD50,BF50,BH50,BJ50,BL50,BN50,BP50,BR50,BT50,BV50,BX50,BZ50,CB50,CD50,CF50)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="I50" s="9"/>
@@ -13850,7 +13848,7 @@
         <v>0.26315789473684209</v>
       </c>
       <c r="H51" s="11">
-        <f>SUM(J51,L51,N51,P51,R51,T51,V51,X51,Z51,AB51,AD51,AF51,AH51,AJ51,AL51,AN51,AP51,AR51,AT51,AV51,AX51,AZ51,BB51,BD51,BF51,BH51,BJ51,BL51,BN51,BP51,BR51,BT51,BV51,BX51,BZ51,CB51,CD51,CF51)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I51" s="9"/>
@@ -14045,7 +14043,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="11">
-        <f>SUM(J52,L52,N52,P52,R52,T52,V52,X52,Z52,AB52,AD52,AF52,AH52,AJ52,AL52,AN52,AP52,AR52,AT52,AV52,AX52,AZ52,BB52,BD52,BF52,BH52,BJ52,BL52,BN52,BP52,BR52,BT52,BV52,BX52,BZ52,CB52,CD52,CF52)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I52" s="9"/>

--- a/data/RPL 6 Predictor Answer Master.xlsx
+++ b/data/RPL 6 Predictor Answer Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckinsey-my.sharepoint.com/personal/vinod_krishnan_external_mckinsey_com/Documents/Desktop/rpl6-predictor-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973018EF-FF06-42E8-B745-77D9E910A011}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91319334-8458-418B-ADC2-253C2CFD8F76}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CEABAB56-9726-4D02-8BFD-74E940918907}"/>
   </bookViews>
@@ -937,16 +937,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1388,14 +1388,14 @@
         <v>213</v>
       </c>
       <c r="N1" s="26"/>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="30"/>
+      <c r="R1" s="28"/>
       <c r="S1" s="25" t="s">
         <v>210</v>
       </c>
@@ -1420,10 +1420,10 @@
         <v>205</v>
       </c>
       <c r="AD1" s="26"/>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="AF1" s="28"/>
+      <c r="AF1" s="30"/>
       <c r="AG1" s="25" t="s">
         <v>203</v>
       </c>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="H33" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>14</v>
@@ -9434,8 +9434,8 @@
       <c r="AG33" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="AH33" s="5">
-        <v>1</v>
+      <c r="AH33" s="14">
+        <v>3</v>
       </c>
       <c r="AI33" s="13" t="s">
         <v>15</v>
@@ -9446,7 +9446,7 @@
       <c r="AK33" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AL33" s="14">
+      <c r="AL33" s="5">
         <v>0</v>
       </c>
       <c r="AM33" s="13" t="s">
@@ -14391,36 +14391,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="BE1:BF1"/>
-    <mergeCell ref="BG1:BH1"/>
-    <mergeCell ref="BI1:BJ1"/>
-    <mergeCell ref="BK1:BL1"/>
-    <mergeCell ref="BM1:BN1"/>
-    <mergeCell ref="BO1:BP1"/>
     <mergeCell ref="CC1:CD1"/>
     <mergeCell ref="CE1:CF1"/>
     <mergeCell ref="BQ1:BR1"/>
@@ -14429,6 +14399,36 @@
     <mergeCell ref="BW1:BX1"/>
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="CA1:CB1"/>
+    <mergeCell ref="BG1:BH1"/>
+    <mergeCell ref="BI1:BJ1"/>
+    <mergeCell ref="BK1:BL1"/>
+    <mergeCell ref="BM1:BN1"/>
+    <mergeCell ref="BO1:BP1"/>
+    <mergeCell ref="AW1:AX1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="BE1:BF1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/RPL 6 Predictor Answer Master.xlsx
+++ b/data/RPL 6 Predictor Answer Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckinsey-my.sharepoint.com/personal/vinod_krishnan_external_mckinsey_com/Documents/Desktop/rpl6-predictor-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91319334-8458-418B-ADC2-253C2CFD8F76}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A339EA1-9C34-49E9-A35E-FA20C2C55160}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CEABAB56-9726-4D02-8BFD-74E940918907}"/>
   </bookViews>
@@ -937,16 +937,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1388,14 +1388,14 @@
         <v>213</v>
       </c>
       <c r="N1" s="26"/>
-      <c r="O1" s="27" t="s">
+      <c r="O1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="28"/>
+      <c r="R1" s="30"/>
       <c r="S1" s="25" t="s">
         <v>210</v>
       </c>
@@ -1420,10 +1420,10 @@
         <v>205</v>
       </c>
       <c r="AD1" s="26"/>
-      <c r="AE1" s="29" t="s">
+      <c r="AE1" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="AF1" s="30"/>
+      <c r="AF1" s="28"/>
       <c r="AG1" s="25" t="s">
         <v>203</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>14</v>
       </c>
       <c r="E21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6">
         <v>22</v>
@@ -8094,7 +8094,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6">
         <v>37</v>
@@ -8584,7 +8584,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6">
         <v>37</v>
@@ -9341,13 +9341,13 @@
         <v>108</v>
       </c>
       <c r="C33" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6">
         <v>36</v>
@@ -9602,7 +9602,7 @@
         <v>19</v>
       </c>
       <c r="E34" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6">
         <v>33</v>
@@ -13118,7 +13118,7 @@
         <v>22</v>
       </c>
       <c r="E48" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6">
         <v>37</v>
@@ -14391,6 +14391,36 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AW1:AX1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="BE1:BF1"/>
+    <mergeCell ref="BG1:BH1"/>
+    <mergeCell ref="BI1:BJ1"/>
+    <mergeCell ref="BK1:BL1"/>
+    <mergeCell ref="BM1:BN1"/>
+    <mergeCell ref="BO1:BP1"/>
     <mergeCell ref="CC1:CD1"/>
     <mergeCell ref="CE1:CF1"/>
     <mergeCell ref="BQ1:BR1"/>
@@ -14399,36 +14429,6 @@
     <mergeCell ref="BW1:BX1"/>
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="CA1:CB1"/>
-    <mergeCell ref="BG1:BH1"/>
-    <mergeCell ref="BI1:BJ1"/>
-    <mergeCell ref="BK1:BL1"/>
-    <mergeCell ref="BM1:BN1"/>
-    <mergeCell ref="BO1:BP1"/>
-    <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="BE1:BF1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/RPL 6 Predictor Answer Master.xlsx
+++ b/data/RPL 6 Predictor Answer Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckinsey-my.sharepoint.com/personal/vinod_krishnan_external_mckinsey_com/Documents/Desktop/rpl6-predictor-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A339EA1-9C34-49E9-A35E-FA20C2C55160}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{BB685A84-0F24-4454-8E2C-F1719BB60E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E76CDED1-54FF-4BCB-B80E-0DF8A814DEF9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CEABAB56-9726-4D02-8BFD-74E940918907}"/>
   </bookViews>
@@ -937,16 +937,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1388,14 +1388,14 @@
         <v>213</v>
       </c>
       <c r="N1" s="26"/>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="30"/>
+      <c r="R1" s="28"/>
       <c r="S1" s="25" t="s">
         <v>210</v>
       </c>
@@ -1420,10 +1420,10 @@
         <v>205</v>
       </c>
       <c r="AD1" s="26"/>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="AF1" s="28"/>
+      <c r="AF1" s="30"/>
       <c r="AG1" s="25" t="s">
         <v>203</v>
       </c>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H16" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="5">
@@ -5142,7 +5142,7 @@
         <v>13</v>
       </c>
       <c r="AH16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="13" t="s">
         <v>4</v>
@@ -14391,36 +14391,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="BE1:BF1"/>
-    <mergeCell ref="BG1:BH1"/>
-    <mergeCell ref="BI1:BJ1"/>
-    <mergeCell ref="BK1:BL1"/>
-    <mergeCell ref="BM1:BN1"/>
-    <mergeCell ref="BO1:BP1"/>
     <mergeCell ref="CC1:CD1"/>
     <mergeCell ref="CE1:CF1"/>
     <mergeCell ref="BQ1:BR1"/>
@@ -14429,6 +14399,36 @@
     <mergeCell ref="BW1:BX1"/>
     <mergeCell ref="BY1:BZ1"/>
     <mergeCell ref="CA1:CB1"/>
+    <mergeCell ref="BG1:BH1"/>
+    <mergeCell ref="BI1:BJ1"/>
+    <mergeCell ref="BK1:BL1"/>
+    <mergeCell ref="BM1:BN1"/>
+    <mergeCell ref="BO1:BP1"/>
+    <mergeCell ref="AW1:AX1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="BE1:BF1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
